--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,119 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2900</v>
+        <v>3400</v>
       </c>
       <c r="E8" s="3">
-        <v>8500</v>
+        <v>13200</v>
       </c>
       <c r="F8" s="3">
         <v>2900</v>
       </c>
       <c r="G8" s="3">
-        <v>2300</v>
+        <v>8500</v>
       </c>
       <c r="H8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>800</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
@@ -797,16 +810,22 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12400</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
@@ -835,8 +854,14 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +876,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -860,37 +887,43 @@
         <v>12300</v>
       </c>
       <c r="E12" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12300</v>
+      </c>
+      <c r="G12" s="3">
         <v>7400</v>
       </c>
-      <c r="F12" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G12" s="3">
-        <v>6400</v>
-      </c>
       <c r="H12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2200</v>
       </c>
       <c r="M12" s="3">
         <v>2800</v>
       </c>
       <c r="N12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,46 +960,58 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>17700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F17" s="3">
         <v>18300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>15100</v>
       </c>
-      <c r="F17" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>11600</v>
-      </c>
       <c r="H17" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="J17" s="3">
         <v>9500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>26100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4200</v>
       </c>
       <c r="M17" s="3">
         <v>5400</v>
       </c>
       <c r="N17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-24800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,108 +1173,122 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>400</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-13400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4900</v>
       </c>
-      <c r="F21" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-6100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-24500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>800</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1220,75 +1299,87 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-13900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-11900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-9100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J23" s="3">
         <v>-6600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-24800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1298,8 +1389,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-14000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-6600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>6200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-14000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1565,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,75 +1962,83 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F41" s="3">
         <v>43300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>66200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>40200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>65500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>70100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>76800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>100200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>112300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>131500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>132300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F42" s="3">
         <v>40200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>21200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>55100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>17400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>5800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1300</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
@@ -1867,46 +2046,58 @@
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F43" s="3">
         <v>9900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>7800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1943,89 +2134,107 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F45" s="3">
         <v>43700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>86900</v>
+      </c>
+      <c r="F46" s="3">
         <v>137000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>103400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>104300</v>
       </c>
-      <c r="G46" s="3">
-        <v>93000</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>92800</v>
+      </c>
+      <c r="J46" s="3">
         <v>85100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>87400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>105800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>115100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>134600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>136200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -2034,92 +2243,104 @@
         <v>0</v>
       </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>20000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>31900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>33900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>17600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>15400</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="E48" s="3">
         <v>1500</v>
       </c>
       <c r="F48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2100</v>
       </c>
       <c r="J48" s="3">
         <v>1900</v>
       </c>
       <c r="K48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>72400</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>73900</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2133,8 +2354,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,34 +2442,40 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -2247,8 +2486,14 @@
       <c r="N52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>400</v>
+      </c>
+      <c r="P52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2530,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>172300</v>
+      </c>
+      <c r="F54" s="3">
         <v>139000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>105500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>106600</v>
       </c>
-      <c r="G54" s="3">
-        <v>115500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>115300</v>
+      </c>
+      <c r="J54" s="3">
         <v>119600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>124300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>125700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>132900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>137200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>138800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,60 +2614,68 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F57" s="3">
         <v>13100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2100</v>
       </c>
       <c r="M57" s="3">
         <v>3000</v>
       </c>
       <c r="N57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>7000</v>
+        <v>37700</v>
       </c>
       <c r="F58" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>4700</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2426,115 +2693,133 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>7100</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>7600</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>8600</v>
       </c>
       <c r="G59" s="3">
-        <v>900</v>
+        <v>7700</v>
       </c>
       <c r="H59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>73700</v>
+      </c>
+      <c r="F60" s="3">
         <v>21700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15600</v>
       </c>
-      <c r="G60" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J60" s="3">
         <v>8400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>38800</v>
+        <v>43000</v>
       </c>
       <c r="E61" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>43900</v>
+      </c>
+      <c r="G61" s="3">
         <v>12700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>12900</v>
-      </c>
-      <c r="G61" s="3">
-        <v>12800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>12800</v>
       </c>
       <c r="I61" s="3">
         <v>12800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2543,48 +2828,60 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11000</v>
+        <v>29600</v>
       </c>
       <c r="E62" s="3">
+        <v>31700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G62" s="3">
         <v>6100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>6700</v>
       </c>
-      <c r="G62" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J62" s="3">
         <v>4500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3006,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>110500</v>
+      </c>
+      <c r="F66" s="3">
         <v>71500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>37000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>35200</v>
       </c>
-      <c r="G66" s="3">
-        <v>29700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>40200</v>
+      </c>
+      <c r="J66" s="3">
         <v>25800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>25000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3200,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3244,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-416400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-399800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-339500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-325400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-320300</v>
       </c>
-      <c r="G72" s="3">
-        <v>-308600</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>-353700</v>
+      </c>
+      <c r="J72" s="3">
         <v>-299600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-292900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-268900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-267000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-264300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-262600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>61900</v>
+      </c>
+      <c r="F76" s="3">
         <v>67500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>68500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>71400</v>
       </c>
-      <c r="G76" s="3">
-        <v>85800</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>75100</v>
+      </c>
+      <c r="J76" s="3">
         <v>93800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>99200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>121500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>127100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>131700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>130700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,34 +3623,36 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -3266,8 +3663,14 @@
       <c r="N83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>16600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,20 +3949,22 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -3542,14 +3983,20 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4077,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-44500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>34000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-17600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-33100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-15400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4143,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,75 +4315,87 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F100" s="3">
         <v>26300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>13800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>39700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
@@ -3906,42 +4403,54 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-22900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-25300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-23400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-12100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-19200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>56300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -781,10 +788,10 @@
         <v>1500</v>
       </c>
       <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3">
         <v>800</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
@@ -816,19 +823,22 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12400</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E12" s="3">
         <v>12300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,38 +983,41 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>17700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1005,13 +1025,16 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E17" s="3">
         <v>23900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18300</v>
       </c>
-      <c r="G17" s="3">
-        <v>15100</v>
-      </c>
       <c r="H17" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I17" s="3">
         <v>16000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6600</v>
       </c>
-      <c r="H18" s="3">
-        <v>-12800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,110 +1208,117 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
-        <v>1700</v>
-      </c>
       <c r="H20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-13100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
@@ -1287,11 +1327,11 @@
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1305,84 +1345,90 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-100</v>
       </c>
       <c r="H24" s="3">
         <v>-100</v>
       </c>
       <c r="I24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-13200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-13200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-13200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,84 +2050,88 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E41" s="3">
         <v>42800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>40200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>70100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>131500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
         <v>9900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>24700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>40200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>55100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1300</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>5</v>
@@ -2052,52 +2142,58 @@
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E43" s="3">
         <v>8300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,104 +2236,113 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E46" s="3">
         <v>62900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>86900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>137000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>103400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>104300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>92800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>85100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>105800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>115100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>134600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>136200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
@@ -2249,22 +2354,22 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>20000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15400</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
@@ -2272,63 +2377,69 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E49" s="3">
         <v>72400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>73900</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>5</v>
@@ -2342,8 +2453,8 @@
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,37 +2565,40 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
         <v>14200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>600</v>
       </c>
       <c r="G52" s="3">
         <v>600</v>
       </c>
       <c r="H52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>700</v>
+      </c>
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E54" s="3">
         <v>151300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>172300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>139000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>105500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>124300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>125700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>132900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>138800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2746,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E57" s="3">
         <v>22800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2669,11 +2803,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>37700</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -2699,121 +2833,130 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E60" s="3">
         <v>29900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E61" s="3">
         <v>43000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>43900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>12800</v>
       </c>
       <c r="J61" s="3">
         <v>12800</v>
@@ -2822,7 +2965,7 @@
         <v>12800</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2834,54 +2977,60 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E62" s="3">
         <v>29600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E66" s="3">
         <v>102500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-436300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-416400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-399800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-339500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-325400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-320300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-353700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-299600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-292900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-268900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-267000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-264300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-262600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E76" s="3">
         <v>48800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>67500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>68500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>71400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>93800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>99200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>121500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>127100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>131700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-13200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,10 +3833,10 @@
         <v>1600</v>
       </c>
       <c r="E83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -3646,16 +3845,16 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-16200</v>
+        <v>-19100</v>
       </c>
       <c r="E89" s="3">
         <v>-16200</v>
       </c>
       <c r="F89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="G89" s="3">
         <v>-4600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3960,14 +4181,14 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3989,14 +4210,17 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>14800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>34000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,84 +4564,90 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>-3600</v>
       </c>
       <c r="E102" s="3">
         <v>-200</v>
       </c>
       <c r="F102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G102" s="3">
         <v>-22900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>56300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,154 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E8" s="3">
         <v>4400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="E9" s="3">
-        <v>1500</v>
+        <v>3600</v>
       </c>
       <c r="F9" s="3">
-        <v>800</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -826,31 +833,34 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="E10" s="3">
-        <v>1900</v>
+        <v>900</v>
       </c>
       <c r="F10" s="3">
-        <v>12400</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+        <v>3300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E12" s="3">
         <v>10500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12300</v>
       </c>
-      <c r="F12" s="3">
-        <v>11200</v>
-      </c>
       <c r="G12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H12" s="3">
         <v>12300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,41 +1003,44 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
-        <v>1400</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>17700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1028,36 +1048,39 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,119 +1242,126 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6100</v>
+        <v>4700</v>
       </c>
       <c r="E20" s="3">
-        <v>4600</v>
+        <v>-5800</v>
       </c>
       <c r="F20" s="3">
-        <v>300</v>
+        <v>-3600</v>
       </c>
       <c r="G20" s="3">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>3800</v>
+        <v>-3700</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>-2100</v>
       </c>
       <c r="J20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>16000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-16200</v>
+        <v>-30500</v>
       </c>
       <c r="E21" s="3">
-        <v>-14400</v>
+        <v>-16500</v>
       </c>
       <c r="F21" s="3">
-        <v>-13600</v>
+        <v>-15300</v>
       </c>
       <c r="G21" s="3">
-        <v>-13400</v>
+        <v>-14000</v>
       </c>
       <c r="H21" s="3">
-        <v>-2400</v>
+        <v>-11600</v>
       </c>
       <c r="I21" s="3">
-        <v>-13100</v>
+        <v>-4100</v>
       </c>
       <c r="J21" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="K21" s="3">
         <v>6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
@@ -1330,11 +1370,11 @@
         <v>200</v>
       </c>
       <c r="K22" s="3">
+        <v>200</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1348,90 +1388,96 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-13900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
       <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6100</v>
+        <v>-4700</v>
       </c>
       <c r="E32" s="3">
-        <v>-4600</v>
+        <v>5800</v>
       </c>
       <c r="F32" s="3">
-        <v>-300</v>
+        <v>3600</v>
       </c>
       <c r="G32" s="3">
-        <v>-1900</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-3800</v>
+        <v>3700</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>2100</v>
       </c>
       <c r="J32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-16000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,91 +2137,95 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E41" s="3">
         <v>39300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>131500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>40200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>21200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1300</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2145,78 +2235,84 @@
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E43" s="3">
         <v>8900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17400</v>
       </c>
-      <c r="G43" s="3">
-        <v>9900</v>
-      </c>
       <c r="H43" s="3">
+        <v>51900</v>
+      </c>
+      <c r="I43" s="3">
         <v>14000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2239,225 +2335,240 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>43700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="M45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E46" s="3">
         <v>60900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>62900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>86900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>137000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>103400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>104300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>92800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>85100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>87400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>115100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>134600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>136200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>6100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>20000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E49" s="3">
         <v>70900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73900</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,40 +2685,43 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>600</v>
       </c>
       <c r="H52" s="3">
         <v>600</v>
       </c>
       <c r="I52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
       </c>
       <c r="K52" s="3">
+        <v>700</v>
+      </c>
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
-      </c>
-      <c r="M52" s="3">
-        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E54" s="3">
         <v>144400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>151300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>172300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>139000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>132900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>138800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,78 +2877,82 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E57" s="3">
         <v>20500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22800</v>
       </c>
-      <c r="F57" s="3">
-        <v>28400</v>
-      </c>
       <c r="G57" s="3">
-        <v>13100</v>
+        <v>14000</v>
       </c>
       <c r="H57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I57" s="3">
         <v>10500</v>
       </c>
-      <c r="I57" s="3">
-        <v>10100</v>
-      </c>
       <c r="J57" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>37700</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2836,130 +2970,139 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10000</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
-        <v>7100</v>
+        <v>2600</v>
       </c>
       <c r="F59" s="3">
-        <v>7600</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3">
-        <v>8600</v>
+        <v>2500</v>
       </c>
       <c r="H59" s="3">
-        <v>7700</v>
+        <v>300</v>
       </c>
       <c r="I59" s="3">
-        <v>5500</v>
+        <v>300</v>
       </c>
       <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E60" s="3">
         <v>30400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>58300</v>
+        <v>59400</v>
       </c>
       <c r="E61" s="3">
-        <v>43000</v>
+        <v>58900</v>
       </c>
       <c r="F61" s="3">
-        <v>5100</v>
+        <v>43700</v>
       </c>
       <c r="G61" s="3">
-        <v>43900</v>
+        <v>5500</v>
       </c>
       <c r="H61" s="3">
-        <v>12700</v>
+        <v>44400</v>
       </c>
       <c r="I61" s="3">
-        <v>12900</v>
+        <v>13300</v>
       </c>
       <c r="J61" s="3">
-        <v>12800</v>
+        <v>13700</v>
       </c>
       <c r="K61" s="3">
         <v>12800</v>
@@ -2968,7 +3111,7 @@
         <v>12800</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -2980,57 +3123,63 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>23200</v>
+        <v>27900</v>
       </c>
       <c r="E62" s="3">
-        <v>29600</v>
+        <v>22600</v>
       </c>
       <c r="F62" s="3">
-        <v>31700</v>
+        <v>28900</v>
       </c>
       <c r="G62" s="3">
+        <v>31200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="H62" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E66" s="3">
         <v>111900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>102500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-469600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-436300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-416400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-399800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-339500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-325400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-320300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-353700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-299600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-292900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-268900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-267000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-264300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-262600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E76" s="3">
         <v>32500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>67500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>68500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>75100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>93800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>99200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>121500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>127100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>131700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>130700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,40 +4022,41 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-16200</v>
       </c>
       <c r="F89" s="3">
         <v>-16200</v>
       </c>
       <c r="G89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="H89" s="3">
         <v>-4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,26 +4392,27 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4213,14 +4434,17 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-44500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>34000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,90 +4810,96 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E100" s="3">
         <v>15300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>26300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F101" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="H101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-200</v>
       </c>
       <c r="F102" s="3">
         <v>-200</v>
       </c>
       <c r="G102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H102" s="3">
         <v>-22900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>56300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,165 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3400</v>
       </c>
-      <c r="G8" s="3">
-        <v>13200</v>
-      </c>
       <c r="H8" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
-        <v>2000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -836,35 +842,38 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3300</v>
       </c>
-      <c r="G10" s="3">
-        <v>11200</v>
-      </c>
       <c r="H10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -886,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E12" s="3">
         <v>10900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12300</v>
       </c>
-      <c r="G12" s="3">
-        <v>10500</v>
-      </c>
       <c r="H12" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I12" s="3">
         <v>12300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,44 +1022,47 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-100</v>
       </c>
       <c r="I14" s="3">
         <v>-100</v>
       </c>
       <c r="J14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>17700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1051,18 +1070,21 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
         <v>1500</v>
@@ -1071,10 +1093,10 @@
         <v>1500</v>
       </c>
       <c r="G15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H15" s="3">
         <v>800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1083,7 +1105,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E17" s="3">
         <v>31000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23900</v>
       </c>
-      <c r="G17" s="3">
-        <v>27900</v>
-      </c>
       <c r="H17" s="3">
+        <v>28100</v>
+      </c>
+      <c r="I17" s="3">
         <v>18300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-14700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-15400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,128 +1275,135 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>16000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-11600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
@@ -1373,11 +1412,11 @@
         <v>200</v>
       </c>
       <c r="L22" s="3">
+        <v>200</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1391,96 +1430,102 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-100</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
       </c>
       <c r="K24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1493,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-10400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-10400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-10400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-10400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,97 +2223,101 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E41" s="3">
         <v>54000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>131500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>132300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E42" s="3">
         <v>35300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>55100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1300</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2238,63 +2327,69 @@
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>2000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
@@ -2314,8 +2409,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2338,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2364,91 +2462,97 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E46" s="3">
         <v>99400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>62900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>137000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>104300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>92800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>85100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>87400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>105800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>115100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>134600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>136200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2464,114 +2568,120 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>20000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E49" s="3">
         <v>75300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>70900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73900</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,43 +2804,46 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E52" s="3">
         <v>9300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>600</v>
       </c>
       <c r="I52" s="3">
         <v>600</v>
       </c>
       <c r="J52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
       </c>
       <c r="L52" s="3">
+        <v>700</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>400</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178100</v>
+      </c>
+      <c r="E54" s="3">
         <v>191600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>144400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>151300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>172300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>139000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>106600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>124300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>125700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>132900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,84 +3007,88 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E57" s="3">
         <v>24500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>600</v>
       </c>
       <c r="F58" s="3">
         <v>600</v>
       </c>
       <c r="G58" s="3">
+        <v>600</v>
+      </c>
+      <c r="H58" s="3">
         <v>38200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2973,30 +3106,33 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
@@ -3005,107 +3141,113 @@
         <v>300</v>
       </c>
       <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E60" s="3">
         <v>34500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E61" s="3">
         <v>59400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>43700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>12800</v>
       </c>
       <c r="L61" s="3">
         <v>12800</v>
@@ -3114,7 +3256,7 @@
         <v>12800</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3126,60 +3268,66 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E62" s="3">
         <v>27900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>5400</v>
       </c>
       <c r="I62" s="3">
         <v>5400</v>
       </c>
       <c r="J62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E66" s="3">
         <v>121800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>111900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>102500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>110500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>71500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-505300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-469600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-436300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-416400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-399800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-339500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-325400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-320300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-353700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-299600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-292900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-268900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-267000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-264300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-262600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E76" s="3">
         <v>69800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>67500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>68500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>75100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>93800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>99200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>121500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>127100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>131700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-10400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,13 +4220,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -4038,28 +4236,28 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -4073,8 +4271,11 @@
       <c r="R83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-16200</v>
       </c>
       <c r="G89" s="3">
         <v>-16200</v>
       </c>
       <c r="H89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>16600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4407,15 +4627,15 @@
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -4437,14 +4657,17 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>34000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4639,8 +4872,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,96 +5055,102 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>64800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>26300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>39700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
@@ -4913,54 +5161,60 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E102" s="3">
         <v>14800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-200</v>
       </c>
       <c r="G102" s="3">
         <v>-200</v>
       </c>
       <c r="H102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-22900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>56300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,174 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E8" s="3">
         <v>12000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -845,38 +852,41 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E10" s="3">
         <v>10700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -898,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="3">
         <v>8300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,47 +1042,50 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-100</v>
       </c>
       <c r="J14" s="3">
         <v>-100</v>
       </c>
       <c r="K14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>17700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1073,13 +1093,16 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1087,7 +1110,7 @@
         <v>1600</v>
       </c>
       <c r="E15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
         <v>1500</v>
@@ -1096,10 +1119,10 @@
         <v>1500</v>
       </c>
       <c r="H15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1108,7 +1131,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E17" s="3">
         <v>27500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,137 +1309,144 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
@@ -1415,11 +1455,11 @@
         <v>200</v>
       </c>
       <c r="M22" s="3">
+        <v>200</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1433,102 +1473,108 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>15400</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-100</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
       </c>
       <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1541,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-33200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,103 +2310,107 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E41" s="3">
         <v>33800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>100200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>112300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>131500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>132300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E42" s="3">
         <v>35700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>24700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>40200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>55100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1300</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2330,70 +2420,76 @@
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E43" s="3">
         <v>10500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2412,8 +2508,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2436,8 +2532,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2465,97 +2564,103 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E46" s="3">
         <v>86000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>99400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>62900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>86900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>137000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>103400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>104300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>92800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>85100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>87400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>105800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>115100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>134600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>136200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E47" s="3">
         <v>6000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2571,120 +2676,126 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>20000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>33900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E49" s="3">
         <v>73700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>75300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,46 +2924,49 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E52" s="3">
         <v>11400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>600</v>
       </c>
       <c r="J52" s="3">
         <v>600</v>
       </c>
       <c r="K52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L52" s="3">
         <v>700</v>
       </c>
       <c r="M52" s="3">
+        <v>700</v>
+      </c>
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>172700</v>
+      </c>
+      <c r="E54" s="3">
         <v>178100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>191600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>144400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>151300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>172300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>139000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>124300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>125700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>132900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>138800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,90 +3138,94 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E57" s="3">
         <v>13100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>600</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
       </c>
       <c r="H58" s="3">
+        <v>600</v>
+      </c>
+      <c r="I58" s="3">
         <v>38200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3109,33 +3243,36 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
@@ -3144,113 +3281,119 @@
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E61" s="3">
         <v>59900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>43700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13700</v>
-      </c>
-      <c r="L61" s="3">
-        <v>12800</v>
       </c>
       <c r="M61" s="3">
         <v>12800</v>
@@ -3259,7 +3402,7 @@
         <v>12800</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3271,63 +3414,69 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E62" s="3">
         <v>44500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>22600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>5400</v>
       </c>
       <c r="J62" s="3">
         <v>5400</v>
       </c>
       <c r="K62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E66" s="3">
         <v>138500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>121800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>111900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-508400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-505300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-469600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-436300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-416400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-399800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-339500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-325400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-320300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-353700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-299600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-292900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-268900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-267000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-264300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-262600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E76" s="3">
         <v>39700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>69800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>67500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>68500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>75100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>93800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>99200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>121500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>127100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>131700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4230,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4239,28 +4438,28 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-16200</v>
       </c>
       <c r="H89" s="3">
         <v>-16200</v>
       </c>
       <c r="I89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,13 +4833,14 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>5</v>
@@ -4630,15 +4851,15 @@
       <c r="G91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -4660,14 +4881,17 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>34000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4875,8 +5109,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,102 +5301,108 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>64800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>39700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-200</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
       </c>
       <c r="I102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-22900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-23400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>56300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,184 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E8" s="3">
         <v>20400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -855,41 +862,44 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E10" s="3">
         <v>19100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,50 +1062,53 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-89600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-100</v>
       </c>
       <c r="K14" s="3">
         <v>-100</v>
       </c>
       <c r="L14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>17700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1096,13 +1116,16 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1113,7 +1136,7 @@
         <v>1600</v>
       </c>
       <c r="F15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="3">
         <v>1500</v>
@@ -1122,10 +1145,10 @@
         <v>1500</v>
       </c>
       <c r="I15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1134,7 +1157,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E17" s="3">
         <v>25800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,120 +1343,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-30500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,25 +1471,25 @@
         <v>2000</v>
       </c>
       <c r="E22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="3">
         <v>2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
@@ -1458,11 +1498,11 @@
         <v>200</v>
       </c>
       <c r="N22" s="3">
+        <v>200</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1476,108 +1516,114 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15400</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-100</v>
       </c>
       <c r="L24" s="3">
         <v>-100</v>
       </c>
       <c r="M24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,109 +2397,113 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E41" s="3">
         <v>37300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>54000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>112300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>131500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>132300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E42" s="3">
         <v>25300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>35300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>55100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2423,76 +2513,82 @@
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E43" s="3">
         <v>12600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>51900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2511,8 +2607,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2535,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2567,103 +2666,109 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>226300</v>
+      </c>
+      <c r="E46" s="3">
         <v>81600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>86000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>99400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>60900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>86900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>137000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>103400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>104300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>92800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>85100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>87400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>105800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>115100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>134600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>136200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E47" s="3">
         <v>6100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2679,32 +2784,35 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>20000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>33900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2712,93 +2820,96 @@
         <v>2100</v>
       </c>
       <c r="E48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E49" s="3">
         <v>72100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>73700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>75300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>70900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,49 +3044,52 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>600</v>
       </c>
       <c r="K52" s="3">
         <v>600</v>
       </c>
       <c r="L52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
       </c>
       <c r="N52" s="3">
+        <v>700</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>256300</v>
+      </c>
+      <c r="E54" s="3">
         <v>172700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>191600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>144400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>151300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>172300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>139000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>105500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>115300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>124300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>125700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>132900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>137200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>138800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,96 +3269,100 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E57" s="3">
         <v>17800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
       </c>
       <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
         <v>38200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3246,36 +3380,39 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>3400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>300</v>
       </c>
       <c r="K59" s="3">
         <v>300</v>
@@ -3284,119 +3421,125 @@
         <v>300</v>
       </c>
       <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E60" s="3">
         <v>27000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>73700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E61" s="3">
         <v>61200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>43700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13700</v>
-      </c>
-      <c r="M61" s="3">
-        <v>12800</v>
       </c>
       <c r="N61" s="3">
         <v>12800</v>
@@ -3405,7 +3548,7 @@
         <v>12800</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3417,66 +3560,72 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E62" s="3">
         <v>43500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5400</v>
       </c>
       <c r="K62" s="3">
         <v>5400</v>
       </c>
       <c r="L62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M62" s="3">
         <v>5900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E66" s="3">
         <v>131700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>138500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>121800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>111900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>102500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-433700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-508400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-505300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-469600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-436300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-416400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-399800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-339500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-325400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-320300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-353700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-299600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-292900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-268900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-267000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-264300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-262600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E76" s="3">
         <v>41000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>69800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>32500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>67500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>68500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>75100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>93800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>99200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>121500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>127100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>131700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>130700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4432,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -4441,28 +4640,28 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-16200</v>
       </c>
       <c r="I89" s="3">
         <v>-16200</v>
       </c>
       <c r="J89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,17 +5054,18 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4854,15 +5075,15 @@
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4884,14 +5105,17 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E94" s="3">
         <v>10500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>14800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>34000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5112,8 +5346,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,108 +5547,114 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>64800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>39700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E102" s="3">
         <v>3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
       </c>
       <c r="I102" s="3">
         <v>-200</v>
       </c>
       <c r="J102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-22900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>56300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,204 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E8" s="3">
         <v>26100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -875,47 +881,50 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E10" s="3">
         <v>24800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="E12" s="3">
         <v>3400</v>
       </c>
       <c r="F12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,56 +1101,59 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-89600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-100</v>
       </c>
       <c r="M14" s="3">
         <v>-100</v>
       </c>
       <c r="N14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>17700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1142,13 +1161,16 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,7 +1178,7 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>1600</v>
@@ -1165,7 +1187,7 @@
         <v>1600</v>
       </c>
       <c r="H15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
         <v>1500</v>
@@ -1174,10 +1196,10 @@
         <v>1500</v>
       </c>
       <c r="K15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L15" s="3">
         <v>800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
@@ -1186,7 +1208,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E17" s="3">
         <v>21900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,164 +1410,171 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-24500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2000</v>
       </c>
       <c r="F22" s="3">
         <v>2000</v>
       </c>
       <c r="G22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3">
         <v>2200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
@@ -1544,11 +1583,11 @@
         <v>200</v>
       </c>
       <c r="P22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1562,120 +1601,126 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>76900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15400</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-100</v>
       </c>
       <c r="N24" s="3">
         <v>-100</v>
       </c>
       <c r="O24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1688,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>74700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>69400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>74700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>74700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,121 +2570,125 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E41" s="3">
         <v>54400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>112300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>131500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E42" s="3">
         <v>145100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>35700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>35300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>55100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1300</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2609,88 +2698,94 @@
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E43" s="3">
         <v>16800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2709,8 +2804,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2733,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2771,115 +2869,121 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E46" s="3">
         <v>225100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>226300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>99400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>60900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>62900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>86900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>137000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>104300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>92800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>85100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>87400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>105800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>115100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>134600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>136200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E47" s="3">
         <v>30900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2895,138 +2999,144 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>20000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>33900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>17600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>15400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2100</v>
       </c>
       <c r="F48" s="3">
         <v>2100</v>
       </c>
       <c r="G48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E49" s="3">
         <v>11400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>75300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>70900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,55 +3283,58 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>600</v>
       </c>
       <c r="M52" s="3">
         <v>600</v>
       </c>
       <c r="N52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O52" s="3">
         <v>700</v>
       </c>
       <c r="P52" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>284700</v>
+      </c>
+      <c r="E54" s="3">
         <v>270100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>256300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>172700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>178100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>191600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>144400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>151300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>172300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>139000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>105500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>115300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>124300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>125700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>132900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>137200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>138800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>11100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3472,37 +3605,37 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
       </c>
       <c r="K58" s="3">
+        <v>600</v>
+      </c>
+      <c r="L58" s="3">
         <v>38200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3520,42 +3653,45 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
-        <v>3200</v>
-      </c>
       <c r="H59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>300</v>
       </c>
       <c r="M59" s="3">
         <v>300</v>
@@ -3564,131 +3700,137 @@
         <v>300</v>
       </c>
       <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
         <v>5800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E60" s="3">
         <v>26100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>73700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E61" s="3">
         <v>62300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>61800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13700</v>
-      </c>
-      <c r="O61" s="3">
-        <v>12800</v>
       </c>
       <c r="P61" s="3">
         <v>12800</v>
@@ -3697,7 +3839,7 @@
         <v>12800</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -3709,72 +3851,78 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E62" s="3">
         <v>48600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>43500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>44500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>28900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>5400</v>
       </c>
       <c r="M62" s="3">
         <v>5400</v>
       </c>
       <c r="N62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O62" s="3">
         <v>5900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>130100</v>
+      </c>
+      <c r="E66" s="3">
         <v>137000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>139000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>131700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>138500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>121800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>111900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>110500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-422100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-434200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-433700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-508400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-505300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-469600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-436300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-416400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-399800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-339500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-325400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-320300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-353700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-299600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-292900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-268900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-267000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-264300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-262600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E76" s="3">
         <v>133200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>117200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>39700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>69800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>61900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>67500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>93800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>99200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>121500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>127100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>131700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>130700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>74700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,17 +5015,18 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
@@ -4836,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -4845,28 +5043,28 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E89" s="3">
         <v>4700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-16200</v>
       </c>
       <c r="K89" s="3">
         <v>-16200</v>
       </c>
       <c r="L89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,23 +5495,24 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5302,15 +5522,15 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5332,14 +5552,17 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>34000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-33100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5586,8 +5819,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,120 +6038,126 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>6500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>64800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>26300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>39700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-200</v>
       </c>
       <c r="K102" s="3">
         <v>-200</v>
       </c>
       <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
         <v>-22900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>56300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>71700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZVRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>ZVRA</t>
   </si>
@@ -656,213 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E8" s="3">
         <v>34100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -884,50 +891,53 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E10" s="3">
         <v>32600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="3">
         <v>2500</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3400</v>
       </c>
       <c r="F12" s="3">
         <v>3400</v>
       </c>
       <c r="G12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,59 +1121,62 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-33100</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-89600</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-100</v>
       </c>
       <c r="N14" s="3">
         <v>-100</v>
       </c>
       <c r="O14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>17700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1164,13 +1184,16 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,7 +1204,7 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>1600</v>
@@ -1190,7 +1213,7 @@
         <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J15" s="3">
         <v>1500</v>
@@ -1199,10 +1222,10 @@
         <v>1500</v>
       </c>
       <c r="L15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
@@ -1211,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E17" s="3">
         <v>24800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E18" s="3">
         <v>9300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,173 +1444,180 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E21" s="3">
         <v>13200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-24500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2000</v>
       </c>
       <c r="G22" s="3">
         <v>2000</v>
       </c>
       <c r="H22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
@@ -1586,11 +1626,11 @@
         <v>200</v>
       </c>
       <c r="Q22" s="3">
+        <v>200</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1604,126 +1644,132 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E23" s="3">
         <v>12700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-100</v>
       </c>
       <c r="O24" s="3">
         <v>-100</v>
       </c>
       <c r="P24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E26" s="3">
         <v>12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E27" s="3">
         <v>11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>69400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E33" s="3">
         <v>12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>74700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E35" s="3">
         <v>12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>74700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,127 +2657,131 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E41" s="3">
         <v>62400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>47700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>54000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>131500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>132300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E42" s="3">
         <v>128600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>154900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>35700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>35300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>24700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>40200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>55100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1300</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2701,94 +2791,100 @@
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E43" s="3">
         <v>23300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>51900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2807,8 +2903,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2872,121 +2971,127 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E46" s="3">
         <v>223000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>225100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>81600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>86000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>99400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>86900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>137000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>103400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>104300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>92800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>85100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>87400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>105800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>115100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>134600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>136200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>87700</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E47" s="3">
         <v>47900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3002,144 +3107,150 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>20000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>33900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>17600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2100</v>
       </c>
       <c r="G48" s="3">
         <v>2100</v>
       </c>
       <c r="H48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E49" s="3">
         <v>11100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>75300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>70900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73900</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,58 +3403,61 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>600</v>
       </c>
       <c r="N52" s="3">
         <v>600</v>
       </c>
       <c r="O52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P52" s="3">
         <v>700</v>
       </c>
       <c r="Q52" s="3">
+        <v>700</v>
+      </c>
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>278600</v>
+      </c>
+      <c r="E54" s="3">
         <v>284700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>270100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>256300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>172700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>178100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>191600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>144400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>151300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>172300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>139000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>105500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>124300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>125700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>132900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>137200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>138800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3608,37 +3742,37 @@
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
       </c>
       <c r="L58" s="3">
+        <v>600</v>
+      </c>
+      <c r="M58" s="3">
         <v>38200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>500</v>
       </c>
       <c r="O58" s="3">
         <v>500</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3656,45 +3790,48 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
@@ -3703,137 +3840,143 @@
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>5800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E60" s="3">
         <v>39300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>700</v>
+      </c>
+      <c r="E61" s="3">
         <v>62800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>61200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>43700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13700</v>
-      </c>
-      <c r="P61" s="3">
-        <v>12800</v>
       </c>
       <c r="Q61" s="3">
         <v>12800</v>
@@ -3842,7 +3985,7 @@
         <v>12800</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -3854,75 +3997,81 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E62" s="3">
         <v>28000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>43500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>44500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>5400</v>
       </c>
       <c r="N62" s="3">
         <v>5400</v>
       </c>
       <c r="O62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P62" s="3">
         <v>5900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E66" s="3">
         <v>130100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>137000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>139000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>131700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>138500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>111900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>102500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>110500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>71500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-384200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-422100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-434200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-433700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-508400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-505300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-469600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-436300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-416400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-399800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-339500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-325400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-320300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-353700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-299600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-292900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-268900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-267000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-264300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-262600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-268800</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E76" s="3">
         <v>154700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>133200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>117200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>41000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>39700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>69800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>32500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>61900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>68500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>93800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>99200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>121500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>127100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>131700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>130700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E81" s="3">
         <v>12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>74700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-47700</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5025,11 +5224,11 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -5037,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -5046,28 +5245,28 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E89" s="3">
         <v>5500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-16200</v>
       </c>
       <c r="L89" s="3">
         <v>-16200</v>
       </c>
       <c r="M89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5505,17 +5726,17 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5525,15 +5746,15 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -5555,14 +5776,17 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>34000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5822,8 +6056,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,126 +6284,132 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>64800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>15300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>26300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>39700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-200</v>
       </c>
       <c r="L102" s="3">
         <v>-200</v>
       </c>
       <c r="M102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N102" s="3">
         <v>-22900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>56300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>71700</v>
       </c>
     </row>
